--- a/data/trans_dic/IP21-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,27; 22,5</t>
+          <t>11,92; 23,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,15</t>
+          <t>6,28; 14,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,34</t>
+          <t>2,58; 8,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,38</t>
+          <t>0,6; 6,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 18,98</t>
+          <t>9,11; 18,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,55</t>
+          <t>4,06; 11,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,5</t>
+          <t>2,5; 8,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,41</t>
+          <t>1,48; 9,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,85</t>
+          <t>11,68; 19,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,42</t>
+          <t>6,4; 11,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,32</t>
+          <t>3,05; 7,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,48</t>
+          <t>1,4; 6,36</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,05</t>
+          <t>0,53; 3,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,34</t>
+          <t>2,88; 7,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,13</t>
+          <t>1,63; 5,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,64</t>
+          <t>1,25; 5,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,81</t>
+          <t>2,12; 5,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,6</t>
+          <t>3,02; 7,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,78</t>
+          <t>0,46; 2,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,07</t>
+          <t>0,7; 3,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,95</t>
+          <t>1,6; 3,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,05</t>
+          <t>3,41; 6,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,54</t>
+          <t>1,24; 3,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,88</t>
+          <t>1,31; 3,9</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,97</t>
+          <t>0,41; 4,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,45</t>
+          <t>0,99; 4,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,28</t>
+          <t>0,34; 3,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,31</t>
+          <t>1,39; 6,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,61</t>
+          <t>0,84; 5,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,39</t>
+          <t>1,18; 5,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,83</t>
+          <t>0,38; 3,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,82</t>
+          <t>1,3; 4,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,06</t>
+          <t>0,76; 3,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,33</t>
+          <t>1,38; 4,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,55</t>
+          <t>0,43; 2,8</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,56</t>
+          <t>0,31; 2,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,19</t>
+          <t>0,38; 3,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,22</t>
+          <t>0,75; 4,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,28</t>
+          <t>0,33; 3,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,54</t>
+          <t>1,38; 5,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,47</t>
+          <t>1,81; 6,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,12</t>
+          <t>0,29; 3,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,37</t>
+          <t>0,35; 2,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,54</t>
+          <t>1,04; 3,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,44</t>
+          <t>1,54; 4,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,18</t>
+          <t>0,32; 2,04</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,03</t>
+          <t>2,7; 4,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,43</t>
+          <t>2,94; 5,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,2</t>
+          <t>2,12; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,27</t>
+          <t>0,75; 2,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,16</t>
+          <t>3,5; 5,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,91</t>
+          <t>3,34; 5,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,02</t>
+          <t>1,9; 3,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,66</t>
+          <t>0,98; 2,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,1</t>
+          <t>3,35; 5,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,15</t>
+          <t>3,51; 5,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,64</t>
+          <t>2,27; 3,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,24</t>
+          <t>1,0; 2,16</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>17658</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14387</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6777</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>34026</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25001</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12580</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4064</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>12660; 24835</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9220; 21264</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3364; 11500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>345; 3802</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11061; 22965</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5864; 16619</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3104; 10579</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>911; 5860</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>26577; 44471</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>18637; 33569</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7774; 19071</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1660; 7540</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3908</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10960</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7032</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9342</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13384</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>13250</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24343</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7744</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1331; 8092</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6794; 17351</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3437; 11872</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1990; 8982</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5376; 15207</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8105; 20305</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1178; 7119</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1271; 7040</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8112; 19505</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>17205; 32305</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5810; 16143</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4469; 13320</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4067</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2776</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5231</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4834</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>524; 5421</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4344</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1876; 8344</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>591; 5925</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1964; 9798</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1325; 9485</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2233; 10691</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>802; 7647</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3490; 12250</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2398; 10272</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5218; 15566</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1662; 10793</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3775</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4622</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7351</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9700</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5033</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>596; 5541</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>654; 5400</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1299; 7510</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4011</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>689; 6816</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2467; 10263</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3153; 11695</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>892; 10874</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1388; 8772</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3655; 12835</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5353; 16266</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1866; 11842</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>25411</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28704</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21228</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>12461</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>58565</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>61926</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>41925</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>21675</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>18367; 34016</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20920; 38098</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14921; 29168</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5003; 15333</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>25312; 42986</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>25045; 42564</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14159; 29730</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7477; 19516</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>47014; 71123</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>51365; 74303</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>32805; 53651</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>14264; 30799</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,92; 23,39</t>
+          <t>11,52; 23,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 14,49</t>
+          <t>6,14; 14,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,82</t>
+          <t>2,74; 9,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,66</t>
+          <t>0,59; 6,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 18,92</t>
+          <t>9,0; 19,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 11,51</t>
+          <t>4,15; 11,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,52</t>
+          <t>2,23; 8,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,54</t>
+          <t>1,64; 9,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 19,54</t>
+          <t>11,4; 19,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 11,53</t>
+          <t>6,28; 11,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,49</t>
+          <t>3,13; 7,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,36</t>
+          <t>1,64; 6,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,2</t>
+          <t>0,54; 3,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,34</t>
+          <t>2,93; 7,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,64</t>
+          <t>1,73; 5,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,64</t>
+          <t>1,22; 5,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,99</t>
+          <t>2,1; 5,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,57</t>
+          <t>3,19; 7,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,76</t>
+          <t>0,51; 3,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,86</t>
+          <t>0,7; 3,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,85</t>
+          <t>1,59; 3,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,4</t>
+          <t>3,37; 6,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,45</t>
+          <t>1,26; 3,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,9</t>
+          <t>1,32; 3,73</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,25</t>
+          <t>0,41; 4,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,42</t>
+          <t>0,88; 4,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,42</t>
+          <t>0,34; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,92</t>
+          <t>1,48; 6,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,98</t>
+          <t>0,83; 5,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,67</t>
+          <t>1,17; 5,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,6</t>
+          <t>0,39; 3,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,55</t>
+          <t>1,3; 4,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,25</t>
+          <t>0,82; 3,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,12</t>
+          <t>1,37; 4,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,8</t>
+          <t>0,5; 2,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,85</t>
+          <t>0,31; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,15</t>
+          <t>0,38; 3,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,33</t>
+          <t>0,76; 4,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,31</t>
+          <t>0,34; 3,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,75</t>
+          <t>1,36; 5,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,72</t>
+          <t>1,77; 6,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,56</t>
+          <t>0,28; 3,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,19</t>
+          <t>0,49; 2,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,67</t>
+          <t>1,11; 3,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,68</t>
+          <t>1,58; 4,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,04</t>
+          <t>0,32; 1,99</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,99</t>
+          <t>2,66; 4,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,36</t>
+          <t>2,86; 5,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,15</t>
+          <t>2,15; 4,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,31</t>
+          <t>0,82; 2,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,95</t>
+          <t>3,36; 5,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,68</t>
+          <t>3,37; 5,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,99</t>
+          <t>1,83; 3,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,56</t>
+          <t>0,97; 2,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,07</t>
+          <t>3,39; 5,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,08</t>
+          <t>3,42; 5,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,71</t>
+          <t>2,25; 3,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,16</t>
+          <t>1,02; 2,09</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12660; 24835</t>
+          <t>12236; 24544</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9220; 21264</t>
+          <t>9011; 20705</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3364; 11500</t>
+          <t>3569; 11925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>345; 3802</t>
+          <t>340; 3487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11061; 22965</t>
+          <t>10922; 23206</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5864; 16619</t>
+          <t>5995; 16866</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3104; 10579</t>
+          <t>2771; 10204</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>911; 5860</t>
+          <t>1008; 6046</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26577; 44471</t>
+          <t>25939; 43470</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18637; 33569</t>
+          <t>18281; 33731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7774; 19071</t>
+          <t>7964; 19011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1660; 7540</t>
+          <t>1948; 7838</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1331; 8092</t>
+          <t>1369; 8486</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6794; 17351</t>
+          <t>6932; 17624</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3437; 11872</t>
+          <t>3640; 12521</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1990; 8982</t>
+          <t>1937; 9435</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5376; 15207</t>
+          <t>5317; 15099</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8105; 20305</t>
+          <t>8548; 20178</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1178; 7119</t>
+          <t>1305; 8010</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1271; 7040</t>
+          <t>1286; 6936</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8112; 19505</t>
+          <t>8067; 19492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17205; 32305</t>
+          <t>17012; 33505</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5810; 16143</t>
+          <t>5908; 16405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4469; 13320</t>
+          <t>4501; 12759</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>524; 5421</t>
+          <t>526; 5353</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>0; 4612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1876; 8344</t>
+          <t>1661; 8625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>591; 5925</t>
+          <t>592; 5876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1964; 9798</t>
+          <t>2091; 9819</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1325; 9485</t>
+          <t>1313; 8741</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2233; 10691</t>
+          <t>2205; 10787</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>802; 7647</t>
+          <t>824; 7395</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3490; 12250</t>
+          <t>3503; 12039</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2398; 10272</t>
+          <t>2573; 10510</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5218; 15566</t>
+          <t>5164; 15559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1662; 10793</t>
+          <t>1923; 10043</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>596; 5541</t>
+          <t>593; 5208</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>654; 5400</t>
+          <t>659; 5472</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1299; 7510</t>
+          <t>1308; 7921</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>0; 3905</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>689; 6816</t>
+          <t>692; 6667</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2467; 10263</t>
+          <t>2437; 9847</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3153; 11695</t>
+          <t>3072; 11872</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>892; 10874</t>
+          <t>855; 9681</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1388; 8772</t>
+          <t>1978; 8805</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3655; 12835</t>
+          <t>3868; 12646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5353; 16266</t>
+          <t>5475; 15919</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1866; 11842</t>
+          <t>1861; 11539</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18367; 34016</t>
+          <t>18081; 33917</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20920; 38098</t>
+          <t>20332; 37653</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14921; 29168</t>
+          <t>15132; 29261</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5003; 15333</t>
+          <t>5478; 15592</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25312; 42986</t>
+          <t>24286; 43268</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25045; 42564</t>
+          <t>25249; 43870</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14159; 29730</t>
+          <t>13633; 29319</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7477; 19516</t>
+          <t>7426; 20256</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47014; 71123</t>
+          <t>47626; 72464</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51365; 74303</t>
+          <t>49961; 76239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32805; 53651</t>
+          <t>32566; 54318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14264; 30799</t>
+          <t>14607; 29838</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,8%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 23,12</t>
+          <t>8,87; 18,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 14,11</t>
+          <t>4,2; 11,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,14</t>
+          <t>2,14; 8,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,11</t>
+          <t>1,88; 10,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 19,12</t>
+          <t>12,27; 22,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 11,68</t>
+          <t>6,46; 14,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,22</t>
+          <t>2,76; 9,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,84</t>
+          <t>0,5; 6,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 19,1</t>
+          <t>11,46; 18,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,58</t>
+          <t>6,37; 11,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,47</t>
+          <t>3,08; 7,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,61</t>
+          <t>1,67; 6,72</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,35</t>
+          <t>2,07; 5,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,46</t>
+          <t>2,97; 7,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,95</t>
+          <t>0,46; 2,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,92</t>
+          <t>0,61; 3,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,95</t>
+          <t>0,52; 3,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,52</t>
+          <t>2,8; 7,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,1</t>
+          <t>1,87; 6,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,8</t>
+          <t>1,1; 6,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,84</t>
+          <t>1,66; 3,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,64</t>
+          <t>3,44; 7,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,5</t>
+          <t>1,3; 3,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,73</t>
+          <t>1,25; 4,05</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,2</t>
+          <t>1,34; 6,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,82; 5,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,57</t>
+          <t>1,13; 5,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,4</t>
+          <t>0,37; 3,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,94</t>
+          <t>0,41; 3,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,51</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,72</t>
+          <t>0,83; 4,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,48</t>
+          <t>0,35; 3,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,47</t>
+          <t>1,25; 4,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,33</t>
+          <t>0,64; 3,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,12</t>
+          <t>1,47; 4,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,6</t>
+          <t>0,42; 2,45</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,68</t>
+          <t>0,34; 3,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,19</t>
+          <t>1,26; 5,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,57</t>
+          <t>1,77; 6,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,44; 3,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,24</t>
+          <t>0,31; 2,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,51</t>
+          <t>0,39; 3,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,82</t>
+          <t>0,72; 4,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,17</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,2</t>
+          <t>0,49; 2,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,61</t>
+          <t>1,08; 3,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,58</t>
+          <t>1,52; 4,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,99</t>
+          <t>0,35; 2,27</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,98</t>
+          <t>3,42; 6,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,29</t>
+          <t>3,31; 5,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,16</t>
+          <t>1,93; 4,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,34</t>
+          <t>0,95; 2,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,99</t>
+          <t>2,72; 5,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,85</t>
+          <t>2,9; 5,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,94</t>
+          <t>2,16; 4,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,66</t>
+          <t>0,77; 2,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,16</t>
+          <t>3,38; 5,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,22</t>
+          <t>3,41; 5,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,75</t>
+          <t>2,22; 3,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,09</t>
+          <t>1,05; 2,24</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16369</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>17658</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>14387</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6777</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16369</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10614</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5803</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3688</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12236; 24544</t>
+          <t>10766; 23032</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9011; 20705</t>
+          <t>6066; 16679</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3569; 11925</t>
+          <t>2656; 10559</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>340; 3487</t>
+          <t>952; 5333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10922; 23206</t>
+          <t>13029; 23887</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5995; 16866</t>
+          <t>9484; 20763</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2771; 10204</t>
+          <t>3598; 12177</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1008; 6046</t>
+          <t>259; 3316</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25939; 43470</t>
+          <t>26072; 42904</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18281; 33731</t>
+          <t>18554; 33264</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7964; 19011</t>
+          <t>7844; 18648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1948; 7838</t>
+          <t>1704; 6871</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9342</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13384</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3908</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10960</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7032</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9342</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13384</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>6949</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1369; 8486</t>
+          <t>5265; 14741</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6932; 17624</t>
+          <t>7964; 20385</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3640; 12521</t>
+          <t>1188; 7162</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1937; 9435</t>
+          <t>960; 6026</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5317; 15099</t>
+          <t>1312; 7724</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8548; 20178</t>
+          <t>6623; 17340</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1305; 8010</t>
+          <t>3926; 12894</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1286; 6936</t>
+          <t>1608; 9243</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8067; 19492</t>
+          <t>8417; 20046</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17012; 33505</t>
+          <t>17363; 35575</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5908; 16405</t>
+          <t>6099; 16587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4501; 12759</t>
+          <t>3785; 12271</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1959</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1343</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4067</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3887</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5276</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4437</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>526; 5353</t>
+          <t>1892; 8923</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4612</t>
+          <t>1299; 8894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1661; 8625</t>
+          <t>2133; 10166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>592; 5876</t>
+          <t>733; 7330</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2091; 9819</t>
+          <t>525; 5064</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1313; 8741</t>
+          <t>0; 4782</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2205; 10787</t>
+          <t>1560; 8400</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>824; 7395</t>
+          <t>616; 5478</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3503; 12039</t>
+          <t>3369; 12956</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2573; 10510</t>
+          <t>2030; 9646</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5164; 15559</t>
+          <t>5562; 16341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1923; 10043</t>
+          <t>1583; 9179</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1887</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3352</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5337</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5086</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>593; 5208</t>
+          <t>696; 6760</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>659; 5472</t>
+          <t>2244; 9890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1308; 7921</t>
+          <t>3084; 11254</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3905</t>
+          <t>1280; 9760</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>692; 6667</t>
+          <t>595; 4960</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2437; 9847</t>
+          <t>662; 5460</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3072; 11872</t>
+          <t>1256; 7317</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>855; 9681</t>
+          <t>0; 4308</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1978; 8805</t>
+          <t>1972; 9474</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3868; 12646</t>
+          <t>3775; 12406</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5475; 15919</t>
+          <t>5279; 15428</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1861; 11539</t>
+          <t>1905; 12485</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>28704</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33222</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18081; 33917</t>
+          <t>24714; 44527</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20332; 37653</t>
+          <t>24790; 44312</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15132; 29261</t>
+          <t>14379; 29947</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5478; 15592</t>
+          <t>6636; 18992</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24286; 43268</t>
+          <t>18554; 34256</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25249; 43870</t>
+          <t>20624; 38603</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13633; 29319</t>
+          <t>15183; 29522</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7426; 20256</t>
+          <t>4829; 14576</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47626; 72464</t>
+          <t>47391; 71554</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49961; 76239</t>
+          <t>49795; 75301</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32566; 54318</t>
+          <t>32181; 52655</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14607; 29838</t>
+          <t>13960; 29765</t>
         </is>
       </c>
     </row>
